--- a/Excel files/contents_tweedie_xgb_results.xlsx
+++ b/Excel files/contents_tweedie_xgb_results.xlsx
@@ -465,13 +465,13 @@
         <v>59911</v>
       </c>
       <c r="C2" t="n">
-        <v>10.76316048198337</v>
+        <v>7.957457959231359</v>
       </c>
       <c r="D2" t="n">
-        <v>33.18393450284589</v>
+        <v>36.2739158084492</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01700856270134032</v>
+        <v>0.01742584834170686</v>
       </c>
     </row>
     <row r="3">
@@ -479,16 +479,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>59912</v>
+        <v>59911</v>
       </c>
       <c r="C3" t="n">
-        <v>19.04537910644036</v>
+        <v>14.61103791382386</v>
       </c>
       <c r="D3" t="n">
-        <v>43.19712411536921</v>
+        <v>45.25628599088648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02108091868073174</v>
+        <v>0.02123149338184974</v>
       </c>
     </row>
     <row r="4">
@@ -496,16 +496,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>59910</v>
+        <v>59911</v>
       </c>
       <c r="C4" t="n">
-        <v>25.38827143697623</v>
+        <v>20.01061699531327</v>
       </c>
       <c r="D4" t="n">
-        <v>48.61969086963779</v>
+        <v>54.53553921650448</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02358537806710065</v>
+        <v>0.02608869823571631</v>
       </c>
     </row>
     <row r="5">
@@ -516,13 +516,13 @@
         <v>59911</v>
       </c>
       <c r="C5" t="n">
-        <v>31.56685239814124</v>
+        <v>25.39102461059833</v>
       </c>
       <c r="D5" t="n">
-        <v>58.48668892190082</v>
+        <v>55.87544774749212</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02755754368980655</v>
+        <v>0.02737393800804527</v>
       </c>
     </row>
     <row r="6">
@@ -533,13 +533,13 @@
         <v>59911</v>
       </c>
       <c r="C6" t="n">
-        <v>38.06567332612915</v>
+        <v>31.19583457778299</v>
       </c>
       <c r="D6" t="n">
-        <v>64.37956351922017</v>
+        <v>64.47582213616865</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03109612592011484</v>
+        <v>0.03039508604429905</v>
       </c>
     </row>
     <row r="7">
@@ -550,13 +550,13 @@
         <v>59911</v>
       </c>
       <c r="C7" t="n">
-        <v>45.41328552058132</v>
+        <v>37.85653713113172</v>
       </c>
       <c r="D7" t="n">
-        <v>70.25420673999767</v>
+        <v>76.29595967351572</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03448448531989117</v>
+        <v>0.03476823955534042</v>
       </c>
     </row>
     <row r="8">
@@ -567,13 +567,13 @@
         <v>59911</v>
       </c>
       <c r="C8" t="n">
-        <v>54.26401626917503</v>
+        <v>45.96273575004838</v>
       </c>
       <c r="D8" t="n">
-        <v>88.63525429386924</v>
+        <v>86.32969738445361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03932499874814308</v>
+        <v>0.03775600474036488</v>
       </c>
     </row>
     <row r="9">
@@ -584,13 +584,13 @@
         <v>59911</v>
       </c>
       <c r="C9" t="n">
-        <v>65.99294537307722</v>
+        <v>56.71617767897615</v>
       </c>
       <c r="D9" t="n">
-        <v>89.67358364907948</v>
+        <v>100.4823157683898</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0416284154829664</v>
+        <v>0.04232945535878219</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         <v>59911</v>
       </c>
       <c r="C10" t="n">
-        <v>84.41693271181639</v>
+        <v>73.66713792331285</v>
       </c>
       <c r="D10" t="n">
-        <v>110.2542406235917</v>
+        <v>102.0029492079919</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04800454006776719</v>
+        <v>0.04763732870424463</v>
       </c>
     </row>
     <row r="11">
@@ -618,13 +618,13 @@
         <v>59911</v>
       </c>
       <c r="C11" t="n">
-        <v>146.0504723204563</v>
+        <v>128.7112896695711</v>
       </c>
       <c r="D11" t="n">
-        <v>171.5697910233513</v>
+        <v>156.7260548146417</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06299344026973344</v>
+        <v>0.06175827477424847</v>
       </c>
     </row>
   </sheetData>
@@ -661,118 +661,118 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>flood_zone</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165937.29296875</v>
+        <v>54276.0830078125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1345883611891663</v>
+        <v>0.09474068015773938</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>solar_panels</t>
+          <t>voluntary_excess</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54374.43017578125</v>
+        <v>18032.49609375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04410199369307139</v>
+        <v>0.03147631240481641</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flood_zone</t>
+          <t>new_business</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52998.3984375</v>
+        <v>16802.056640625</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04298592235500014</v>
+        <v>0.02932854004870884</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>accidental_damage_cover</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44798.8271484375</v>
+        <v>16461.27856445312</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03633541695922699</v>
+        <v>0.0287337007579899</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>voluntary_excess</t>
+          <t>sum_insured</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39529.69091796875</v>
+        <v>15497.33251953125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03206172779958279</v>
+        <v>0.02705110137221411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>elevation_m</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38077.19091796875</v>
+        <v>14539.95874023438</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03088363461070524</v>
+        <v>0.02537997409129526</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>prior_claims_5y</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37565.1728515625</v>
+        <v>14487.22705078125</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03046834717757927</v>
+        <v>0.02528792920065832</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>marketing_segment</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33230.70751953125</v>
+        <v>13859.8173828125</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02695275056133699</v>
+        <v>0.02419276508072091</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sum_insured</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33191.8916015625</v>
+        <v>12916.626953125</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02692126776024989</v>
+        <v>0.02254639530097829</v>
       </c>
     </row>
     <row r="11">
@@ -782,127 +782,127 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32091.4501953125</v>
+        <v>12571.28076171875</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02602872213170465</v>
+        <v>0.02194358221553505</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>accidental_damage_cover</t>
+          <t>missed_payments_12m</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29227.77978515625</v>
+        <v>12385.48828125</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02370605734313647</v>
+        <v>0.02161927535711144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>elevation_m</t>
+          <t>marketing_segment</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28948.2998046875</v>
+        <v>11947.04345703125</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02347937681892451</v>
+        <v>0.02085395555958394</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26878.5927734375</v>
+        <v>11808.62817382812</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02180067956833063</v>
+        <v>0.02061234715035141</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>credit_band</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25318.2021484375</v>
+        <v>11665.50659179688</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02053507848929387</v>
+        <v>0.02036252374240687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>licence_points</t>
+          <t>distance_to_river_km</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24071.453125</v>
+        <v>11164.06127929688</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0195238657300846</v>
+        <v>0.01948723452963664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bedrooms</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22563.19262695312</v>
+        <v>10977.85009765625</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01830054633607283</v>
+        <v>0.01916219681460717</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>energy_rating</t>
+          <t>works_from_home</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22390.1708984375</v>
+        <v>10826.84594726562</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01816021193339326</v>
+        <v>0.01889861412547704</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>distance_to_river_km</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22312.6357421875</v>
+        <v>10736.15258789062</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01809732474614597</v>
+        <v>0.01874030589693849</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>new_business</t>
+          <t>credit_band</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21891.35595703125</v>
+        <v>10660.25415039062</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01775563328624623</v>
+        <v>0.01860782268899173</v>
       </c>
     </row>
     <row r="21">
@@ -912,387 +912,387 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20756.99194335938</v>
+        <v>10157.10205078125</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01683557372121033</v>
+        <v>0.01772955422343342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lodgers</t>
+          <t>security_level</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20676.78247070312</v>
+        <v>10155.92041015625</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01677051745035333</v>
+        <v>0.01772749163102972</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rainfall_mm</t>
+          <t>wildfire_index</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18970.58544921875</v>
+        <v>10146.16674804688</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01538665577056406</v>
+        <v>0.01771046629443463</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wildfire_index</t>
+          <t>energy_rating</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>18653.52294921875</v>
+        <v>9979.647216796875</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01512949282963567</v>
+        <v>0.0174198009999641</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>prior_claims_5y</t>
+          <t>policyholder_age</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>18604.3486328125</v>
+        <v>9970.03515625</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01508960854238891</v>
+        <v>0.01740302283353309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>rainfall_mm</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>18323.77807617188</v>
+        <v>9902.17138671875</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01486204347403924</v>
+        <v>0.01728456440162058</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>freezing_days</t>
+          <t>basement</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18025.0263671875</v>
+        <v>9889.7783203125</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01461973204304438</v>
+        <v>0.01726293189839814</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hail_days</t>
+          <t>mean_temperature_c</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17645.38208007812</v>
+        <v>9786.896240234375</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01431181028824932</v>
+        <v>0.01708334785875324</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>year_built</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>17391.41357421875</v>
+        <v>9761.397705078125</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01410582160188626</v>
+        <v>0.01703883933068976</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>soil_type</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>17226.39916992188</v>
+        <v>9743.2548828125</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01397198177691632</v>
+        <v>0.01700717044033931</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>year_built</t>
+          <t>dry_summer_index</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17041.138671875</v>
+        <v>9713.94970703125</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01382172075735207</v>
+        <v>0.01695601729641664</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>bedrooms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17019.6240234375</v>
+        <v>9636.87890625</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0138042706638682</v>
+        <v>0.01682148768997348</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mean_temperature_c</t>
+          <t>bicycle_cover</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16917.90014648438</v>
+        <v>9612.704833984375</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01372176449754483</v>
+        <v>0.01677929105525505</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>renewal_count</t>
+          <t>days_quote_to_inception</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16846.1455078125</v>
+        <v>9603.41796875</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01366356577046069</v>
+        <v>0.01676308052789052</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>policyholder_age</t>
+          <t>renewal_count</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16802.4130859375</v>
+        <v>9527.0087890625</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01362809529311539</v>
+        <v>0.01662970580273125</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>security_level</t>
+          <t>freezing_days</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>16705.05908203125</v>
+        <v>9516.833251953125</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01354913344188516</v>
+        <v>0.01661194406950938</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>days_quote_to_inception</t>
+          <t>wind_exposure_index</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16514.56689453125</v>
+        <v>9490.2646484375</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01339462910548024</v>
+        <v>0.01656556770208528</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>soil_type</t>
+          <t>branch_id</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16207.01489257812</v>
+        <v>9416.929443359375</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01314517993596105</v>
+        <v>0.01643755870026381</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>years_at_address</t>
+          <t>trees_within_5m</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16002.64233398438</v>
+        <v>9407.54052734375</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0129794175130538</v>
+        <v>0.01642117003991896</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>branch_id</t>
+          <t>years_at_address</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15170.87719726562</v>
+        <v>9197.491943359375</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01230478973865506</v>
+        <v>0.01605452335854394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tenure</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>14959.75366210938</v>
+        <v>9119.3603515625</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01213355173605311</v>
+        <v>0.01591814210664745</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dry_summer_index</t>
+          <t>solar_panels</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>14469.177734375</v>
+        <v>8982.699951171875</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01173565558521583</v>
+        <v>0.0156795969028277</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>works_from_home</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14334.1083984375</v>
+        <v>8945.664794921875</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01162610359575339</v>
+        <v>0.015614950824879</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>missed_payments_12m</t>
+          <t>roof_type</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13410.3984375</v>
+        <v>8802.192626953125</v>
       </c>
       <c r="C44" t="n">
-        <v>0.01087690124568192</v>
+        <v>0.01536451545770063</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>basement</t>
+          <t>listed_building</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12513.55834960938</v>
+        <v>8655.0361328125</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01014949250278602</v>
+        <v>0.01510764897854619</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>wind_exposure_index</t>
+          <t>hail_days</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>12330.2958984375</v>
+        <v>8580.742919921875</v>
       </c>
       <c r="C46" t="n">
-        <v>0.01000085205837803</v>
+        <v>0.01497796774271809</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>bicycle_cover</t>
+          <t>exposure</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>12208.58129882812</v>
+        <v>8511.260009765625</v>
       </c>
       <c r="C47" t="n">
-        <v>0.009902131823757199</v>
+        <v>0.01485668304782596</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>roof_type</t>
+          <t>lodgers</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10986.90576171875</v>
+        <v>8510.661865234375</v>
       </c>
       <c r="C48" t="n">
-        <v>0.008911255659015798</v>
+        <v>0.01485563896696046</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>trees_within_5m</t>
+          <t>licence_points</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10934.08569335938</v>
+        <v>8301.030029296875</v>
       </c>
       <c r="C49" t="n">
-        <v>0.008868414376557811</v>
+        <v>0.01448971973294765</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>listed_building</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9879.324096679688</v>
+        <v>8250.973022460938</v>
       </c>
       <c r="C50" t="n">
-        <v>0.008012918711884517</v>
+        <v>0.01440234358840135</v>
       </c>
     </row>
   </sheetData>
@@ -1352,10 +1352,10 @@
         <v>149778</v>
       </c>
       <c r="D2" t="n">
-        <v>3385.284402960878</v>
+        <v>61.5609909186367</v>
       </c>
       <c r="E2" t="n">
-        <v>54.4777946472168</v>
+        <v>44.98476028442383</v>
       </c>
       <c r="F2" t="n">
         <v>74.90190515295971</v>
@@ -1372,10 +1372,10 @@
         <v>149778</v>
       </c>
       <c r="D3" t="n">
-        <v>6599.7583835008</v>
+        <v>64.42727851525615</v>
       </c>
       <c r="E3" t="n">
-        <v>51.58128356933594</v>
+        <v>43.91439437866211</v>
       </c>
       <c r="F3" t="n">
         <v>79.30739875015023</v>
@@ -1392,10 +1392,10 @@
         <v>149777</v>
       </c>
       <c r="D4" t="n">
-        <v>7446.237556882636</v>
+        <v>63.63996796239112</v>
       </c>
       <c r="E4" t="n">
-        <v>51.20210647583008</v>
+        <v>43.96543121337891</v>
       </c>
       <c r="F4" t="n">
         <v>77.50122882685594</v>
@@ -1412,10 +1412,10 @@
         <v>149777</v>
       </c>
       <c r="D5" t="n">
-        <v>13177.39367665237</v>
+        <v>64.88143857766813</v>
       </c>
       <c r="E5" t="n">
-        <v>51.12556076049805</v>
+        <v>43.96735000610352</v>
       </c>
       <c r="F5" t="n">
         <v>79.59107199369728</v>

--- a/Excel files/contents_tweedie_xgb_results.xlsx
+++ b/Excel files/contents_tweedie_xgb_results.xlsx
@@ -462,16 +462,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C2" t="n">
-        <v>7.957457959231359</v>
+        <v>6.101307979351274</v>
       </c>
       <c r="D2" t="n">
-        <v>36.2739158084492</v>
+        <v>35.57859191818409</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01742584834170686</v>
+        <v>0.01370527424406197</v>
       </c>
     </row>
     <row r="3">
@@ -479,16 +479,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C3" t="n">
-        <v>14.61103791382386</v>
+        <v>14.97134581333197</v>
       </c>
       <c r="D3" t="n">
-        <v>45.25628599088648</v>
+        <v>45.26179346470442</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02123149338184974</v>
+        <v>0.01974723538704581</v>
       </c>
     </row>
     <row r="4">
@@ -496,16 +496,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>59911</v>
+        <v>72161</v>
       </c>
       <c r="C4" t="n">
-        <v>20.01061699531327</v>
+        <v>22.00317578556872</v>
       </c>
       <c r="D4" t="n">
-        <v>54.53553921650448</v>
+        <v>56.09892587408711</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02608869823571631</v>
+        <v>0.02426518479511093</v>
       </c>
     </row>
     <row r="5">
@@ -513,16 +513,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C5" t="n">
-        <v>25.39102461059833</v>
+        <v>28.88669961634657</v>
       </c>
       <c r="D5" t="n">
-        <v>55.87544774749212</v>
+        <v>67.46552853302292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02737393800804527</v>
+        <v>0.02735511765194978</v>
       </c>
     </row>
     <row r="6">
@@ -530,16 +530,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C6" t="n">
-        <v>31.19583457778299</v>
+        <v>36.24645774516765</v>
       </c>
       <c r="D6" t="n">
-        <v>64.47582213616865</v>
+        <v>77.42365316925806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03039508604429905</v>
+        <v>0.03069482553144314</v>
       </c>
     </row>
     <row r="7">
@@ -547,16 +547,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>59911</v>
+        <v>72161</v>
       </c>
       <c r="C7" t="n">
-        <v>37.85653713113172</v>
+        <v>44.69665133769293</v>
       </c>
       <c r="D7" t="n">
-        <v>76.29595967351572</v>
+        <v>89.21943889358518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03476823955534042</v>
+        <v>0.034727900112249</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +564,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C8" t="n">
-        <v>45.96273575004838</v>
+        <v>55.09704786600734</v>
       </c>
       <c r="D8" t="n">
-        <v>86.32969738445361</v>
+        <v>92.69141445636207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03775600474036488</v>
+        <v>0.0370139408552978</v>
       </c>
     </row>
     <row r="9">
@@ -581,16 +581,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>59911</v>
+        <v>72161</v>
       </c>
       <c r="C9" t="n">
-        <v>56.71617767897615</v>
+        <v>69.3213235673729</v>
       </c>
       <c r="D9" t="n">
-        <v>100.4823157683898</v>
+        <v>116.5741069275648</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04232945535878219</v>
+        <v>0.04283477224539571</v>
       </c>
     </row>
     <row r="10">
@@ -598,16 +598,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C10" t="n">
-        <v>73.66713792331285</v>
+        <v>92.4845570065068</v>
       </c>
       <c r="D10" t="n">
-        <v>102.0029492079919</v>
+        <v>139.7716471272969</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04763732870424463</v>
+        <v>0.04836340456195782</v>
       </c>
     </row>
     <row r="11">
@@ -615,16 +615,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>59911</v>
+        <v>72162</v>
       </c>
       <c r="C11" t="n">
-        <v>128.7112896695711</v>
+        <v>182.734296816712</v>
       </c>
       <c r="D11" t="n">
-        <v>156.7260548146417</v>
+        <v>257.9618983675619</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06175827477424847</v>
+        <v>0.06141736648097337</v>
       </c>
     </row>
   </sheetData>
@@ -665,127 +665,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54276.0830078125</v>
+        <v>116994.396484375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09474068015773938</v>
+        <v>0.1480474413109092</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>voluntary_excess</t>
+          <t>sum_insured</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18032.49609375</v>
+        <v>25959.27099609375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03147631240481641</v>
+        <v>0.03284946770746794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>new_business</t>
+          <t>exposure</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16802.056640625</v>
+        <v>25396.603515625</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02932854004870884</v>
+        <v>0.0321374551385294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>accidental_damage_cover</t>
+          <t>elevation_m</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16461.27856445312</v>
+        <v>24110.29833984375</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0287337007579899</v>
+        <v>0.03050973453188627</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sum_insured</t>
+          <t>prior_claims_5y</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15497.33251953125</v>
+        <v>20805.078125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02705110137221411</v>
+        <v>0.02632723169003382</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>elevation_m</t>
+          <t>voluntary_excess</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14539.95874023438</v>
+        <v>20090.99267578125</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02537997409129526</v>
+        <v>0.02542361128759595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>prior_claims_5y</t>
+          <t>accidental_damage_cover</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14487.22705078125</v>
+        <v>19060.64794921875</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02528792920065832</v>
+        <v>0.02411978901046544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>new_business</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13859.8173828125</v>
+        <v>18428.08520507812</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02419276508072091</v>
+        <v>0.02331932934271431</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12916.626953125</v>
+        <v>17512.83862304688</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02254639530097829</v>
+        <v>0.02216115494539283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>urban_density</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12571.28076171875</v>
+        <v>17337.43701171875</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02194358221553505</v>
+        <v>0.0219391976505201</v>
       </c>
     </row>
     <row r="12">
@@ -795,49 +795,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12385.48828125</v>
+        <v>17064.59619140625</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02161927535711144</v>
+        <v>0.02159393850524274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>marketing_segment</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11947.04345703125</v>
+        <v>16899.34716796875</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02085395555958394</v>
+        <v>0.0213848285321654</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>channel</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11808.62817382812</v>
+        <v>16275.41430664062</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02061234715035141</v>
+        <v>0.02059528931964627</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>urban_density</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11665.50659179688</v>
+        <v>15670.4267578125</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02036252374240687</v>
+        <v>0.01982972394796692</v>
       </c>
     </row>
     <row r="16">
@@ -847,101 +847,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11164.06127929688</v>
+        <v>15248.58251953125</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01948723452963664</v>
+        <v>0.01929591239813231</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tenure</t>
+          <t>channel</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10977.85009765625</v>
+        <v>15148.85815429688</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01916219681460717</v>
+        <v>0.01916971885764701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>works_from_home</t>
+          <t>marketing_segment</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10826.84594726562</v>
+        <v>14634.77197265625</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01889861412547704</v>
+        <v>0.01851918219869383</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>property_type</t>
+          <t>high_value_items</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10736.15258789062</v>
+        <v>14600.46240234375</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01874030589693849</v>
+        <v>0.01847576606723901</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>credit_band</t>
+          <t>security_level</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10660.25415039062</v>
+        <v>13898.99682617188</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01860782268899173</v>
+        <v>0.01758811514684815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>high_value_items</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10157.10205078125</v>
+        <v>13390.68139648438</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01772955422343342</v>
+        <v>0.01694488093217241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>security_level</t>
+          <t>works_from_home</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10155.92041015625</v>
+        <v>12926.31567382812</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01772749163102972</v>
+        <v>0.01635726170306744</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wildfire_index</t>
+          <t>credit_band</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10146.16674804688</v>
+        <v>12462.19384765625</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01771046629443463</v>
+        <v>0.01576995110626916</v>
       </c>
     </row>
     <row r="24">
@@ -951,23 +951,23 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9979.647216796875</v>
+        <v>12348.73706054688</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0174198009999641</v>
+        <v>0.01562638023847001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>policyholder_age</t>
+          <t>wildfire_index</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9970.03515625</v>
+        <v>12037.09838867188</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01740302283353309</v>
+        <v>0.01523202538583581</v>
       </c>
     </row>
     <row r="26">
@@ -977,36 +977,36 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>9902.17138671875</v>
+        <v>11940.77783203125</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01728456440162058</v>
+        <v>0.01511013910422922</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>basement</t>
+          <t>dry_summer_index</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9889.7783203125</v>
+        <v>11939.32739257812</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01726293189839814</v>
+        <v>0.01510830368427524</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mean_temperature_c</t>
+          <t>policyholder_age</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9786.896240234375</v>
+        <v>11895.93188476562</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01708334785875324</v>
+        <v>0.01505338999533727</v>
       </c>
     </row>
     <row r="29">
@@ -1016,179 +1016,179 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>9761.397705078125</v>
+        <v>11856.04711914062</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01703883933068976</v>
+        <v>0.01500291888154461</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>soil_type</t>
+          <t>renewal_count</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9743.2548828125</v>
+        <v>11790.44995117188</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01700717044033931</v>
+        <v>0.01491991069340192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dry_summer_index</t>
+          <t>soil_type</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9713.94970703125</v>
+        <v>11695.02563476562</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01695601729641664</v>
+        <v>0.0147991585351165</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bedrooms</t>
+          <t>mean_temperature_c</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9636.87890625</v>
+        <v>11654.06201171875</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01682148768997348</v>
+        <v>0.01474732220994922</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bicycle_cover</t>
+          <t>branch_id</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9612.704833984375</v>
+        <v>11630.095703125</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01677929105525505</v>
+        <v>0.01471699468340442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>days_quote_to_inception</t>
+          <t>trees_within_5m</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9603.41796875</v>
+        <v>11606.298828125</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01676308052789052</v>
+        <v>0.01468688156208569</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>renewal_count</t>
+          <t>roof_type</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9527.0087890625</v>
+        <v>11506.9140625</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01662970580273125</v>
+        <v>0.01456111775887627</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>freezing_days</t>
+          <t>wind_exposure_index</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9516.833251953125</v>
+        <v>11421.51342773438</v>
       </c>
       <c r="C36" t="n">
-        <v>0.01661194406950938</v>
+        <v>0.01445304980140733</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>wind_exposure_index</t>
+          <t>years_at_address</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9490.2646484375</v>
+        <v>11351.28686523438</v>
       </c>
       <c r="C37" t="n">
-        <v>0.01656556770208528</v>
+        <v>0.01436418346932129</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>branch_id</t>
+          <t>bicycle_cover</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9416.929443359375</v>
+        <v>11345.47924804688</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01643755870026381</v>
+        <v>0.01435683437491542</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>trees_within_5m</t>
+          <t>freezing_days</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9407.54052734375</v>
+        <v>11290.6533203125</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01642117003991896</v>
+        <v>0.01428745636569037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>years_at_address</t>
+          <t>bedrooms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9197.491943359375</v>
+        <v>11249.88134765625</v>
       </c>
       <c r="C40" t="n">
-        <v>0.01605452335854394</v>
+        <v>0.01423586255940272</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>days_quote_to_inception</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9119.3603515625</v>
+        <v>11221.60888671875</v>
       </c>
       <c r="C41" t="n">
-        <v>0.01591814210664745</v>
+        <v>0.01420008592712684</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>solar_panels</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8982.699951171875</v>
+        <v>11193.09350585938</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0156795969028277</v>
+        <v>0.01416400189830927</v>
       </c>
     </row>
     <row r="43">
@@ -1198,101 +1198,101 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8945.664794921875</v>
+        <v>11142.8974609375</v>
       </c>
       <c r="C43" t="n">
-        <v>0.015614950824879</v>
+        <v>0.01410048265091007</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>roof_type</t>
+          <t>lodgers</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8802.192626953125</v>
+        <v>11001.48120117188</v>
       </c>
       <c r="C44" t="n">
-        <v>0.01536451545770063</v>
+        <v>0.0139215312135149</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>listed_building</t>
+          <t>basement</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>8655.0361328125</v>
+        <v>10928.2607421875</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01510764897854619</v>
+        <v>0.01382887633490544</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hail_days</t>
+          <t>licence_points</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8580.742919921875</v>
+        <v>10618.92358398438</v>
       </c>
       <c r="C46" t="n">
-        <v>0.01497796774271809</v>
+        <v>0.01343743387141551</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>exposure</t>
+          <t>solar_panels</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>8511.260009765625</v>
+        <v>10546.91479492188</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01485668304782596</v>
+        <v>0.01334631226821955</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>lodgers</t>
+          <t>listed_building</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>8510.661865234375</v>
+        <v>10476.41625976562</v>
       </c>
       <c r="C48" t="n">
-        <v>0.01485563896696046</v>
+        <v>0.01325710177558332</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>licence_points</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8301.030029296875</v>
+        <v>10327.05688476562</v>
       </c>
       <c r="C49" t="n">
-        <v>0.01448971973294765</v>
+        <v>0.01306809893468658</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>hail_days</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>8250.973022460938</v>
+        <v>10316.83544921875</v>
       </c>
       <c r="C50" t="n">
-        <v>0.01440234358840135</v>
+        <v>0.01305516449145928</v>
       </c>
     </row>
   </sheetData>
@@ -1346,19 +1346,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>449332</v>
+        <v>541212</v>
       </c>
       <c r="C2" t="n">
-        <v>149778</v>
+        <v>180405</v>
       </c>
       <c r="D2" t="n">
-        <v>61.5609909186367</v>
+        <v>72.26913283256648</v>
       </c>
       <c r="E2" t="n">
-        <v>44.98476028442383</v>
+        <v>54.17994156039506</v>
       </c>
       <c r="F2" t="n">
-        <v>74.90190515295971</v>
+        <v>100.8771266871761</v>
       </c>
     </row>
     <row r="3">
@@ -1366,19 +1366,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>449332</v>
+        <v>541213</v>
       </c>
       <c r="C3" t="n">
-        <v>149778</v>
+        <v>180404</v>
       </c>
       <c r="D3" t="n">
-        <v>64.42727851525615</v>
+        <v>71.07636589135015</v>
       </c>
       <c r="E3" t="n">
-        <v>43.91439437866211</v>
+        <v>55.5151134835377</v>
       </c>
       <c r="F3" t="n">
-        <v>79.30739875015023</v>
+        <v>98.5748705682801</v>
       </c>
     </row>
     <row r="4">
@@ -1386,19 +1386,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>449333</v>
+        <v>541213</v>
       </c>
       <c r="C4" t="n">
-        <v>149777</v>
+        <v>180404</v>
       </c>
       <c r="D4" t="n">
-        <v>63.63996796239112</v>
+        <v>69.39466769533249</v>
       </c>
       <c r="E4" t="n">
-        <v>43.96543121337891</v>
+        <v>56.57198702737813</v>
       </c>
       <c r="F4" t="n">
-        <v>77.50122882685594</v>
+        <v>93.55601538768541</v>
       </c>
     </row>
     <row r="5">
@@ -1406,19 +1406,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>449333</v>
+        <v>541213</v>
       </c>
       <c r="C5" t="n">
-        <v>149777</v>
+        <v>180404</v>
       </c>
       <c r="D5" t="n">
-        <v>64.88143857766813</v>
+        <v>71.12102656059928</v>
       </c>
       <c r="E5" t="n">
-        <v>43.96735000610352</v>
+        <v>54.75027415921868</v>
       </c>
       <c r="F5" t="n">
-        <v>79.59107199369728</v>
+        <v>98.21094454668412</v>
       </c>
     </row>
   </sheetData>
